--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.43834253101774</v>
+        <v>9.496230661290383</v>
       </c>
       <c r="D2" t="n">
-        <v>46.19794367718113</v>
+        <v>7.507165847541934</v>
       </c>
       <c r="E2" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F2" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.35177226232876</v>
+        <v>2.657162992628424</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54615733677663</v>
+        <v>3.013750567226202</v>
       </c>
       <c r="E3" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F3" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.69716915981014</v>
+        <v>3.525789988469148</v>
       </c>
       <c r="D4" t="n">
-        <v>23.53583735883301</v>
+        <v>3.824573570810364</v>
       </c>
       <c r="E4" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F4" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.938594558297</v>
+        <v>1.940021615723262</v>
       </c>
       <c r="D5" t="n">
-        <v>13.88793195270195</v>
+        <v>2.256788942314067</v>
       </c>
       <c r="E5" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F5" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>23.98422985586042</v>
+        <v>3.897437351577318</v>
       </c>
       <c r="D6" t="n">
-        <v>23.708619565425</v>
+        <v>3.852650679381563</v>
       </c>
       <c r="E6" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F6" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2.664731615897284</v>
+        <v>0.4330188875833086</v>
       </c>
       <c r="D7" t="n">
-        <v>2.29238087299498</v>
+        <v>0.3725118918616843</v>
       </c>
       <c r="E7" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F7" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>11.00290854514269</v>
+        <v>1.787972638585687</v>
       </c>
       <c r="D8" t="n">
-        <v>11.41022299440367</v>
+        <v>1.854161236590597</v>
       </c>
       <c r="E8" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F8" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>18.25685837745299</v>
+        <v>2.966739486336111</v>
       </c>
       <c r="D9" t="n">
-        <v>16.76818011212367</v>
+        <v>2.724829268220097</v>
       </c>
       <c r="E9" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F9" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.37951754609603</v>
+        <v>4.611671601240605</v>
       </c>
       <c r="D10" t="n">
-        <v>26.95546367026081</v>
+        <v>4.380262846417383</v>
       </c>
       <c r="E10" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F10" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>33.41211042977061</v>
+        <v>5.429467944837723</v>
       </c>
       <c r="D11" t="n">
-        <v>31.20527635259357</v>
+        <v>5.070857407296455</v>
       </c>
       <c r="E11" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F11" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>32.81645616706367</v>
+        <v>5.332674127147847</v>
       </c>
       <c r="D12" t="n">
-        <v>30.70964868815204</v>
+        <v>4.990317911824707</v>
       </c>
       <c r="E12" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F12" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.75055992308283</v>
+        <v>6.94696598750096</v>
       </c>
       <c r="D13" t="n">
-        <v>40.76684078323409</v>
+        <v>6.624611627275541</v>
       </c>
       <c r="E13" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F13" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>65.30840131236286</v>
+        <v>10.61261521325897</v>
       </c>
       <c r="D14" t="n">
-        <v>64.06624567665266</v>
+        <v>10.41076492245606</v>
       </c>
       <c r="E14" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F14" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>68.50391992131244</v>
+        <v>11.13188698721327</v>
       </c>
       <c r="D15" t="n">
-        <v>66.38393549705535</v>
+        <v>10.78738951827149</v>
       </c>
       <c r="E15" t="n">
-        <v>19.94492724979623</v>
+        <v>3.241050678091888</v>
       </c>
       <c r="F15" t="n">
-        <v>18.19231542481274</v>
+        <v>2.95625125653207</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
